--- a/90411_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90411_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -107,90 +73,72 @@
     <t>% TOT</t>
   </si>
   <si>
+    <t>50-004-011-001941</t>
+  </si>
+  <si>
+    <t>Fiorentina Frollata</t>
+  </si>
+  <si>
     <t>50-004-011-000750</t>
   </si>
   <si>
     <t>Punta Di Petto (Con Patate)</t>
   </si>
   <si>
-    <t>50-004-011-001941</t>
-  </si>
-  <si>
-    <t>Fiorentina Frollata</t>
-  </si>
-  <si>
     <t>50-004-011-000730</t>
   </si>
   <si>
     <t>Stinco Di Suino (Con Patate)</t>
   </si>
   <si>
+    <t>50-004-011-001370</t>
+  </si>
+  <si>
+    <t>Verdure Grigliate</t>
+  </si>
+  <si>
+    <t>50-004-011-001490</t>
+  </si>
+  <si>
+    <t>Controfiletto chianina</t>
+  </si>
+  <si>
+    <t>50-004-011-000720</t>
+  </si>
+  <si>
+    <t>Spuntature Di Suino</t>
+  </si>
+  <si>
+    <t>50-004-011-000860</t>
+  </si>
+  <si>
+    <t>Patate Al Forno</t>
+  </si>
+  <si>
     <t>50-004-011-000600</t>
   </si>
   <si>
     <t>Grigliata Mista</t>
   </si>
   <si>
-    <t>50-004-011-001490</t>
-  </si>
-  <si>
-    <t>Controfiletto chianina</t>
-  </si>
-  <si>
     <t>50-004-011-000610</t>
   </si>
   <si>
     <t>Grigliata Mista Xxl</t>
   </si>
   <si>
-    <t>50-004-011-000860</t>
-  </si>
-  <si>
-    <t>Patate Al Forno</t>
-  </si>
-  <si>
-    <t>50-004-011-001370</t>
-  </si>
-  <si>
-    <t>Verdure Grigliate</t>
-  </si>
-  <si>
-    <t>50-004-011-000720</t>
-  </si>
-  <si>
-    <t>Spuntature Di Suino</t>
-  </si>
-  <si>
-    <t>50-004-011-000640</t>
-  </si>
-  <si>
-    <t>Hamburger Di Chianina (Con Patate)</t>
-  </si>
-  <si>
     <t>50-004-011-000670</t>
   </si>
   <si>
     <t>Spiedini Misti</t>
   </si>
   <si>
-    <t>50-004-011-000590</t>
-  </si>
-  <si>
-    <t>Filetto Bovino adulto</t>
-  </si>
-  <si>
     <t>50-004-011-000710</t>
   </si>
   <si>
     <t>Etrusca Marinata Birra (Con Patate)</t>
   </si>
   <si>
-    <t>50-004-011-000770</t>
-  </si>
-  <si>
-    <t>Battuta Al Coltello B.A.</t>
-  </si>
-  <si>
     <t>50-004-011-000660</t>
   </si>
   <si>
@@ -203,12 +151,6 @@
     <t>Contorno Del Giorno</t>
   </si>
   <si>
-    <t>50-004-011-000560</t>
-  </si>
-  <si>
-    <t>Arrosticini Di Pecora</t>
-  </si>
-  <si>
     <t>50-004-011-002110</t>
   </si>
   <si>
@@ -234,21 +176,6 @@
   </si>
   <si>
     <t>12:00-15:59</t>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
   </si>
 </sst>
 </file>
@@ -386,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -399,27 +326,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -507,115 +420,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>25.2727</v>
+      <c r="B11" t="n" s="1">
+        <v>535.79</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>41.5454</v>
+      <c r="B12" t="n" s="1">
+        <v>769.95</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>9.0909</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>95.7272</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>161.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>58.9999</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>927.43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>1620.15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-42.76</v>
+      <c r="B13" t="n" s="1">
+        <v>-30.41</v>
       </c>
     </row>
   </sheetData>
@@ -625,11 +450,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.65234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.72265625" customWidth="true" bestFit="true"/>
@@ -637,356 +462,288 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>199.7272</v>
+        <v>139.9728</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>13.0</v>
+        <v>2.44</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>21.54</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>139.9728</v>
+        <v>107.5454</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>2.44</v>
+        <v>7.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>15.09</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>101.0909</v>
+        <v>50.5455</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>10.9</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>86.7271</v>
+        <v>36.3637</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>9.35</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>72.7272</v>
+        <v>36.3636</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>7.84</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>70.6364</v>
+        <v>29.7273</v>
       </c>
       <c r="D7" t="n" s="5">
         <v>3.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>7.62</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>58.1818</v>
+        <v>29.0909</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>6.27</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>45.4546</v>
+        <v>28.909</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>39.6364</v>
+        <v>23.5455</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>25.2727</v>
+        <v>19.8182</v>
       </c>
       <c r="D11" t="n" s="5">
         <v>2.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>19.8182</v>
+        <v>15.3636</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>2.14</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>19.0909</v>
+        <v>9.9091</v>
       </c>
       <c r="D13" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>15.3636</v>
+        <v>7.2728</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>10.8182</v>
+        <v>0.9091</v>
       </c>
       <c r="D15" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>9.9091</v>
+        <v>0.4545</v>
       </c>
       <c r="D16" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>1.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C17" t="n" s="5">
-        <v>7.2728</v>
-      </c>
-      <c r="D17" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E17" t="n" s="5">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>62</v>
-      </c>
-      <c r="B18" t="s" s="4">
-        <v>63</v>
-      </c>
-      <c r="C18" t="n" s="7">
-        <v>4.3636</v>
-      </c>
-      <c r="D18" t="n" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="E18" t="n" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="C19" t="n" s="5">
-        <v>0.9091</v>
-      </c>
-      <c r="D19" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E19" t="n" s="5">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s" s="4">
-        <v>67</v>
-      </c>
-      <c r="C20" t="n" s="7">
-        <v>0.4545</v>
-      </c>
-      <c r="D20" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E20" t="n" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="1">
-        <v>68</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" t="n" s="1">
-        <v>927.43</v>
-      </c>
-      <c r="D21" t="n" s="1">
-        <v>83.44</v>
-      </c>
-      <c r="E21" t="n" s="1">
+      <c r="A17" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="n" s="1">
+        <v>535.79</v>
+      </c>
+      <c r="D17" t="n" s="1">
+        <v>45.44</v>
+      </c>
+      <c r="E17" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -997,24 +754,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.65234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="31.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1022,15 +779,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>1.0</v>
@@ -1041,10 +798,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>1.0</v>
@@ -1055,10 +812,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n" s="1">
         <v>2.0</v>
@@ -1070,15 +827,15 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>8.0</v>
@@ -1089,10 +846,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>8.0</v>
@@ -1103,10 +860,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>7.0</v>
@@ -1117,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>3.0</v>
@@ -1131,10 +888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>3.0</v>
@@ -1145,10 +902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>2.44</v>
@@ -1159,10 +916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>2.0</v>
@@ -1173,10 +930,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>2.0</v>
@@ -1187,10 +944,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>2.0</v>
@@ -1201,10 +958,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>1.0</v>
@@ -1215,10 +972,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>1.0</v>
@@ -1229,10 +986,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>1.0</v>
@@ -1243,10 +1000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>1.0</v>
@@ -1257,10 +1014,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>1.0</v>
@@ -1271,10 +1028,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>1.0</v>
@@ -1285,10 +1042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="1">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n" s="1">
         <v>43.44</v>
@@ -1298,305 +1055,13 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" t="s" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="4">
-        <v>62</v>
-      </c>
-      <c r="B26" t="s" s="4">
-        <v>63</v>
-      </c>
-      <c r="C26" t="n" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="D26" t="n" s="7">
-        <v>4.3636</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C27" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D27" t="n" s="5">
-        <v>25.2727</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="4">
-        <v>44</v>
-      </c>
-      <c r="B28" t="s" s="4">
-        <v>45</v>
-      </c>
-      <c r="C28" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D28" t="n" s="7">
-        <v>9.0909</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C29" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D29" t="n" s="5">
-        <v>19.0909</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="4">
-        <v>36</v>
-      </c>
-      <c r="B30" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="C30" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D30" t="n" s="7">
-        <v>14.4545</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C31" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D31" t="n" s="5">
-        <v>3.6364</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="B32" t="s" s="4">
-        <v>71</v>
-      </c>
-      <c r="C32" t="n" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D32" t="n" s="1">
-        <v>75.91</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="s" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C35" t="n" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D35" t="n" s="5">
-        <v>25.4545</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B36" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C36" t="n" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="D36" t="n" s="7">
-        <v>92.1818</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C37" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D37" t="n" s="5">
-        <v>43.3636</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B38" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C38" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D38" t="n" s="7">
-        <v>47.0909</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C39" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D39" t="n" s="5">
-        <v>36.3636</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="4">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s" s="4">
-        <v>49</v>
-      </c>
-      <c r="C40" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D40" t="n" s="7">
-        <v>25.2727</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C41" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D41" t="n" s="5">
-        <v>25.2727</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="4">
-        <v>56</v>
-      </c>
-      <c r="B42" t="s" s="4">
-        <v>57</v>
-      </c>
-      <c r="C42" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D42" t="n" s="7">
-        <v>10.8182</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C43" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D43" t="n" s="5">
-        <v>9.9091</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="B44" t="s" s="4">
-        <v>71</v>
-      </c>
-      <c r="C44" t="n" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D44" t="n" s="1">
-        <v>315.73</v>
-      </c>
-    </row>
-    <row r="45"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>75</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>76</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>2856.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>3342.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>